--- a/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE/b. Resultados de Aprendizaje a nivel microcurricular/F5_Verificacion_Syllabus_Investigacion_vs_Profundizacion.xlsx
+++ b/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE/b. Resultados de Aprendizaje a nivel microcurricular/F5_Verificacion_Syllabus_Investigacion_vs_Profundizacion.xlsx
@@ -1749,7 +1749,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>0c09ab38c8</t>
+          <t>20563eb1bd</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>71e61fd2cd</t>
+          <t>5035d0a615</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>3567632207</t>
+          <t>2676b955f4</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>e8e128d410</t>
+          <t>5a873debe8</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>30ec98b43c</t>
+          <t>4d15f16797</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
